--- a/public/files/p4-p6-curriculum-gap-map.xlsx
+++ b/public/files/p4-p6-curriculum-gap-map.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D95"/>
+  <dimension ref="A1:D91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -459,7 +459,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>P4–P6 課程覆蓋工作簿</t>
+          <t>⚠️ 本頁全部示例均為虛構，不涉及任何真實學校或個人</t>
         </is>
       </c>
     </row>
@@ -473,28 +473,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>• 在「空白覆蓋表」按科目與學期填寫現有的 AI 素養活動。</t>
+          <t>• 在「空白覆蓋表」按科目與學期填寫現有的 AI 素養活動</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>• 對照下方的「P4–P6 階段目標」，標出已覆蓋、重複與空白。</t>
+          <t>• 對照下方的「P4–P6 階段目標」，標出已覆蓋、重複與空白</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>• 在「缺口與下一步」表為每個缺口寫下最小的下一步與負責人。</t>
+          <t>• 在「缺口與下一步」表為每個缺口寫下最小的下一步與負責人</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>• 用「會議核對清單」檢查是否讀得出下一步，再翻到後頁對照三個虛構示例。</t>
+          <t>• 用「會議核對清單」檢查是否讀得出下一步，再翻到後頁對照三個虛構示例</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>注意： 以下目標列為本工作簿的建議骨架，並非架構本身的原文； 引用前請先與 F（《中小學人工智能素養學習架構》pp.1-6 to 1-10）所列的 P4–P6 階段目標逐項核對。</t>
+          <t>注意： 以下目標列為本工作簿的建議骨架，並非架構本身的原文； 引用前請先與 F（《中小學人工智能素養學習架構》pp.1-6 to 1-10）所列的 P4–P6 階段目標逐項核對</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>建議的 P4–P6 目標（請與 F pp.1-6 to 1-10 核對）</t>
+          <t>建議的 P4–P6 目標（請與官方文件的學習進程核對）</t>
         </is>
       </c>
     </row>
@@ -835,7 +835,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>□ 活動能對應 EDB 框架（F pp.1-6 to 1-10 或 B p.2）</t>
+          <t>□ 活動能對應官方文件的規劃要求或學習進程</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>以下三個學校均為虛構，僅作示範。判斷欄的「已覆蓋／部分覆蓋／空白」是根據上面的 建議目標清單標出，並非 EDB 對任何學校的評價。</t>
+          <t>以下三個學校均為虛構，僅作示範。判斷欄的「已覆蓋／部分覆蓋／空白」是根據上面的 建議目標清單標出，並非對任何學校的評價</t>
         </is>
       </c>
     </row>
@@ -1318,21 +1318,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>核心判斷：從零開始的學校先做 G2 與 G3 兩項試點；「下學期再議」也是一個合法的下一步， 前提是會議真的訂出了檢討日期。</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>與 EDB 框架的關係</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>對應 F（《中小學人工智能素養學習架構》，pp.1-6 to 1-10）：跨科實施與四個學習階段的進程， 供學校把本科活動對照到階段目標；以及 B（《中小學數字教育發展藍圖》單張，p.2）： 在學校發展計劃中加入數碼與 AI 教育策略，並附清晰的實施時間表。</t>
+          <t>核心判斷：從零開始的學校先做 G2 與 G3 兩項試點；「下學期再議」也是一個合法的下一步， 前提是會議真的訂出了檢討日期</t>
         </is>
       </c>
     </row>

--- a/public/files/p4-p6-curriculum-gap-map.xlsx
+++ b/public/files/p4-p6-curriculum-gap-map.xlsx
@@ -463,6 +463,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -470,6 +471,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -477,6 +479,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -484,6 +487,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -491,6 +495,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
@@ -498,6 +503,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
@@ -505,6 +511,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
@@ -512,10 +519,11 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>目標編號</t>
+          <t>目標編號 Goal</t>
         </is>
       </c>
       <c r="B17" s="1" t="inlineStr">
@@ -596,6 +604,7 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
@@ -603,10 +612,11 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>科目</t>
+          <t>科目 Subject</t>
         </is>
       </c>
       <c r="B27" s="1" t="inlineStr">
@@ -725,6 +735,7 @@
       <c r="C37" s="2" t="inlineStr"/>
       <c r="D37" s="2" t="inlineStr"/>
     </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
@@ -732,25 +743,26 @@
         </is>
       </c>
     </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>缺口（哪個目標未覆蓋）</t>
+          <t>缺口（哪個目標未覆蓋） Gap (which goal is not covered)</t>
         </is>
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>最小的下一步</t>
+          <t>最小的下一步 Smallest next step</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>負責人</t>
+          <t>負責人 Owner</t>
         </is>
       </c>
       <c r="D41" s="1" t="inlineStr">
         <is>
-          <t>日期／學期</t>
+          <t>日期／學期 Dates / term</t>
         </is>
       </c>
     </row>
@@ -790,6 +802,7 @@
       <c r="C47" s="2" t="inlineStr"/>
       <c r="D47" s="2" t="inlineStr"/>
     </row>
+    <row r="48"/>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
@@ -797,6 +810,7 @@
         </is>
       </c>
     </row>
+    <row r="50"/>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
@@ -804,6 +818,7 @@
         </is>
       </c>
     </row>
+    <row r="52"/>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
@@ -811,6 +826,7 @@
         </is>
       </c>
     </row>
+    <row r="54"/>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
@@ -818,6 +834,7 @@
         </is>
       </c>
     </row>
+    <row r="56"/>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
@@ -825,6 +842,7 @@
         </is>
       </c>
     </row>
+    <row r="58"/>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
@@ -832,6 +850,7 @@
         </is>
       </c>
     </row>
+    <row r="60"/>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
@@ -839,6 +858,7 @@
         </is>
       </c>
     </row>
+    <row r="62"/>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
@@ -846,6 +866,7 @@
         </is>
       </c>
     </row>
+    <row r="64"/>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
@@ -853,6 +874,7 @@
         </is>
       </c>
     </row>
+    <row r="66"/>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
@@ -1007,6 +1029,7 @@
         </is>
       </c>
     </row>
+    <row r="74"/>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
@@ -1161,6 +1184,7 @@
         </is>
       </c>
     </row>
+    <row r="82"/>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
@@ -1315,6 +1339,7 @@
         </is>
       </c>
     </row>
+    <row r="90"/>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
